--- a/data/trans_dic/P32B-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P32B-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se ha sentido mal o culpable por su forma de beber</t>
+          <t>Población que se ha sentido mal o culpable por su forma de beber (tasa de respuesta: 99,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,01</t>
+          <t>0,0; 2,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,23; 5,33</t>
+          <t>1,29; 5,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 5,41</t>
+          <t>0,75; 5,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,84; 6,7</t>
+          <t>0,87; 6,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,12</t>
+          <t>0,0; 4,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,73</t>
+          <t>0,0; 2,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,41</t>
+          <t>0,3; 3,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,86</t>
+          <t>0,22; 1,98</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,87; 3,76</t>
+          <t>0,89; 3,8</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,83</t>
+          <t>0,68; 3,53</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,96; 4,54</t>
+          <t>0,94; 4,6</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,39</t>
+          <t>0,0; 2,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,28</t>
+          <t>0,0; 1,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 4,11</t>
+          <t>0,39; 4,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,01</t>
+          <t>0,0; 1,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,52</t>
+          <t>0,0; 4,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,84</t>
+          <t>0,0; 4,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,89</t>
+          <t>0,0; 3,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 4,94</t>
+          <t>0,73; 5,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,14</t>
+          <t>0,25; 2,21</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,18</t>
+          <t>0,25; 2,17</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,59</t>
+          <t>0,43; 2,54</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,3</t>
+          <t>0,47; 2,21</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,94</t>
+          <t>0,0; 1,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,25; 7,26</t>
+          <t>2,25; 6,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,95</t>
+          <t>0,86; 3,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 4,97</t>
+          <t>0,53; 4,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3,09</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,47</t>
+          <t>0,0; 12,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,64</t>
+          <t>0,0; 1,48</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,8; 5,8</t>
+          <t>1,8; 5,41</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,86</t>
+          <t>0,99; 4,13</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,01</t>
+          <t>0,54; 4,55</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,61</t>
+          <t>0,55; 2,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,17; 5,05</t>
+          <t>2,12; 5,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,28; 4,04</t>
+          <t>1,31; 4,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,15; 4,36</t>
+          <t>1,09; 4,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,69</t>
+          <t>0,47; 4,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,33</t>
+          <t>0,0; 2,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,18</t>
+          <t>0,33; 3,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,66</t>
+          <t>0,0; 1,63</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,46</t>
+          <t>0,77; 2,63</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,67; 3,91</t>
+          <t>1,59; 3,87</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,13</t>
+          <t>1,26; 3,2</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,7</t>
+          <t>0,63; 2,69</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,12</t>
+          <t>0,0; 2,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,5; 3,11</t>
+          <t>0,57; 3,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,82; 4,06</t>
+          <t>0,72; 3,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,4; 5,58</t>
+          <t>1,34; 5,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,81</t>
+          <t>0,0; 4,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,62</t>
+          <t>0,0; 4,07</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,79; 4,9</t>
+          <t>0,75; 4,75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,37</t>
+          <t>0,26; 2,62</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,72</t>
+          <t>0,57; 2,66</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,53</t>
+          <t>0,45; 2,49</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,4; 4,45</t>
+          <t>1,58; 4,56</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,3</t>
+          <t>0,0; 4,76</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,09; 9,48</t>
+          <t>2,14; 10,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,58; 5,68</t>
+          <t>0,6; 5,89</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,89</t>
+          <t>0,0; 2,33</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,79</t>
+          <t>0,0; 2,21</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,5</t>
+          <t>0,4; 3,59</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,41</t>
+          <t>0,0; 9,39</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,97</t>
+          <t>0,0; 2,06</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,99; 3,89</t>
+          <t>1,01; 4,2</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,64</t>
+          <t>0,87; 3,41</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,18</t>
+          <t>0,0; 4,88</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,33</t>
+          <t>0,48; 1,34</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,18; 3,74</t>
+          <t>2,16; 3,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,56; 2,86</t>
+          <t>1,51; 2,84</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,3; 2,93</t>
+          <t>1,31; 3,07</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,82</t>
+          <t>0,51; 2,02</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,4</t>
+          <t>0,28; 1,3</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,71</t>
+          <t>0,52; 1,68</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,16</t>
+          <t>0,55; 2,13</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,6; 1,31</t>
+          <t>0,57; 1,33</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,63; 2,72</t>
+          <t>1,6; 2,66</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,22</t>
+          <t>1,28; 2,22</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,16; 2,38</t>
+          <t>1,13; 2,34</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se ha sentido mal o culpable por su forma de beber</t>
+          <t>Población que se ha sentido mal o culpable por su forma de beber (tasa de respuesta: 99,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5813</t>
+          <t>0; 5845</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3614; 15644</t>
+          <t>3793; 15918</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2984; 15635</t>
+          <t>2175; 15579</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2378; 18852</t>
+          <t>2462; 18667</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5278</t>
+          <t>0; 5961</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 2103</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4210</t>
+          <t>0; 4594</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>496; 5557</t>
+          <t>488; 5513</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>916; 7774</t>
+          <t>925; 8263</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3872; 16648</t>
+          <t>3931; 16809</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3806; 16936</t>
+          <t>3006; 15610</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4244; 20153</t>
+          <t>4181; 20451</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5337</t>
+          <t>0; 4906</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5784</t>
+          <t>0; 4086</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>946; 9830</t>
+          <t>943; 10049</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4278</t>
+          <t>0; 3878</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 6961</t>
+          <t>0; 7108</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 6894</t>
+          <t>0; 6696</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 5529</t>
+          <t>0; 6925</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>965; 6580</t>
+          <t>975; 7314</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>967; 8084</t>
+          <t>948; 8336</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>995; 8624</t>
+          <t>987; 8589</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1869; 11159</t>
+          <t>1843; 10935</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1588; 7950</t>
+          <t>1612; 7663</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 6576</t>
+          <t>0; 6374</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8736; 28202</t>
+          <t>8745; 25577</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2067; 13088</t>
+          <t>2858; 12701</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1265; 10494</t>
+          <t>1120; 9990</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 1907</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 2059</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 7404</t>
+          <t>0; 6686</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 1119</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 6571</t>
+          <t>0; 5945</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8406; 27055</t>
+          <t>8383; 25235</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3918; 14905</t>
+          <t>3823; 15974</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1108; 10078</t>
+          <t>1353; 11458</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4357; 17480</t>
+          <t>3703; 17902</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14396; 33523</t>
+          <t>14039; 34065</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8447; 26628</t>
+          <t>8645; 26605</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5845; 22215</t>
+          <t>5567; 22316</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>931; 9019</t>
+          <t>903; 8440</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 5341</t>
+          <t>0; 4904</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1001; 9464</t>
+          <t>995; 9543</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 6867</t>
+          <t>0; 6744</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6324; 21210</t>
+          <t>6657; 22701</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14883; 34924</t>
+          <t>14167; 34599</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11847; 29914</t>
+          <t>12013; 30564</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6124; 24927</t>
+          <t>5811; 24855</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4569</t>
+          <t>0; 4343</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1530; 9443</t>
+          <t>1748; 9970</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2610; 12860</t>
+          <t>2279; 12394</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3236; 12896</t>
+          <t>3092; 13058</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 6751</t>
+          <t>0; 6873</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 6698</t>
+          <t>0; 7538</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 1991</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1030; 6424</t>
+          <t>981; 6233</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>904; 8429</t>
+          <t>907; 9298</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2951; 13317</t>
+          <t>2787; 13034</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2778; 12834</t>
+          <t>2286; 12645</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5057; 16107</t>
+          <t>5734; 16521</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 6004</t>
+          <t>0; 6641</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2884; 13101</t>
+          <t>2955; 13819</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>938; 9208</t>
+          <t>969; 9540</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 4530</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 4113</t>
+          <t>0; 5072</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 7346</t>
+          <t>0; 5813</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>965; 8860</t>
+          <t>1019; 9083</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 11422</t>
+          <t>0; 11404</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 7037</t>
+          <t>0; 7371</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3967; 15631</t>
+          <t>4055; 16872</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3684; 15085</t>
+          <t>3615; 14141</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 11196</t>
+          <t>0; 10555</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>8882; 24929</t>
+          <t>8948; 25199</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>44512; 76288</t>
+          <t>44044; 76677</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>31091; 57030</t>
+          <t>30077; 56671</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>20111; 45152</t>
+          <t>20221; 47255</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4061; 16261</t>
+          <t>4583; 18108</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3055; 14656</t>
+          <t>2974; 13654</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6456; 19578</t>
+          <t>5975; 19137</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>5185; 21668</t>
+          <t>5560; 21367</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>16622; 36305</t>
+          <t>15911; 36824</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>50303; 83879</t>
+          <t>49438; 82172</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>39854; 69706</t>
+          <t>40081; 69770</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>29504; 60480</t>
+          <t>28806; 59548</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P32B-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P32B-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -717,27 +717,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,02</t>
+          <t>0,0; 2,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,29; 5,42</t>
+          <t>1,28; 5,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,75; 5,39</t>
+          <t>1,03; 5,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,87; 6,63</t>
+          <t>1,09; 6,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,65</t>
+          <t>0,0; 3,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -747,32 +747,32 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,98</t>
+          <t>0,0; 3,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,39</t>
+          <t>0,31; 3,34</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,98</t>
+          <t>0,22; 1,84</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,8</t>
+          <t>0,85; 3,78</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,53</t>
+          <t>0,7; 3,46</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,94; 4,6</t>
+          <t>1,23; 5,03</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,2</t>
+          <t>0,0; 2,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,61</t>
+          <t>0,0; 1,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 4,2</t>
+          <t>0,39; 4,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,82</t>
+          <t>0,0; 2,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,62</t>
+          <t>0,0; 4,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,7</t>
+          <t>0,0; 5,28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,62</t>
+          <t>0,0; 2,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,73; 5,49</t>
+          <t>0,98; 6,04</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,21</t>
+          <t>0,0; 2,15</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,17</t>
+          <t>0,25; 2,45</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,54</t>
+          <t>0,44; 2,66</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,21</t>
+          <t>0,74; 2,87</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -997,22 +997,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,88</t>
+          <t>0,0; 1,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,25; 6,59</t>
+          <t>2,15; 6,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,83</t>
+          <t>0,66; 3,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,53; 4,73</t>
+          <t>0,85; 6,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,16</t>
+          <t>0,0; 11,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1037,22 +1037,22 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,48</t>
+          <t>0,0; 1,57</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,8; 5,41</t>
+          <t>1,72; 5,37</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,99; 4,13</t>
+          <t>0,99; 3,93</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 4,55</t>
+          <t>0,82; 5,52</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,67</t>
+          <t>0,64; 2,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,12; 5,13</t>
+          <t>2,0; 5,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,31; 4,04</t>
+          <t>1,31; 4,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,09; 4,38</t>
+          <t>0,94; 3,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,39</t>
+          <t>0,49; 4,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,14</t>
+          <t>0,0; 2,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,21</t>
+          <t>0,34; 2,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,63</t>
+          <t>0,46; 5,92</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,63</t>
+          <t>0,67; 2,45</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,87</t>
+          <t>1,65; 3,77</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,2</t>
+          <t>1,2; 3,21</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,69</t>
+          <t>1,08; 3,49</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -1277,32 +1277,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,02</t>
+          <t>0,0; 1,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,28</t>
+          <t>0,56; 3,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,92</t>
+          <t>0,67; 4,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,34; 5,65</t>
+          <t>1,47; 5,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,9</t>
+          <t>0,0; 5,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,07</t>
+          <t>0,0; 4,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1312,34 +1312,34 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,75; 4,75</t>
+          <t>0,77; 4,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,62</t>
+          <t>0,25; 2,35</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,66</t>
+          <t>0,57; 2,72</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,49</t>
+          <t>0,44; 2,51</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,58; 4,56</t>
+          <t>1,51; 4,54</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1384,27 +1384,27 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
           <t>1,83%</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -1417,17 +1417,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,76</t>
+          <t>0,0; 4,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,14; 10,0</t>
+          <t>2,15; 9,39</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,6; 5,89</t>
+          <t>0,59; 5,75</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1437,42 +1437,42 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,33</t>
+          <t>0,0; 3,12</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,21</t>
+          <t>0,0; 2,36</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,59</t>
+          <t>0,37; 3,43</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,39</t>
+          <t>0,0; 9,2</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,06</t>
+          <t>0,0; 2,05</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,01; 4,2</t>
+          <t>1,19; 4,38</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,87; 3,41</t>
+          <t>0,87; 3,34</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,88</t>
+          <t>0,0; 5,31</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,34</t>
+          <t>0,47; 1,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,16; 3,76</t>
+          <t>2,16; 3,85</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,51; 2,84</t>
+          <t>1,56; 2,95</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,31; 3,07</t>
+          <t>1,45; 3,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,02</t>
+          <t>0,55; 1,97</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,3</t>
+          <t>0,29; 1,39</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,68</t>
+          <t>0,59; 1,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,13</t>
+          <t>1,08; 2,89</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,33</t>
+          <t>0,57; 1,31</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,6; 2,66</t>
+          <t>1,62; 2,72</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,22</t>
+          <t>1,31; 2,23</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,13; 2,34</t>
+          <t>1,51; 2,79</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7343</t>
+          <t>9065</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9287</t>
+          <t>11070</t>
         </is>
       </c>
     </row>
@@ -1927,27 +1927,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5845</t>
+          <t>0; 5812</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3793; 15918</t>
+          <t>3767; 16542</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2175; 15579</t>
+          <t>2962; 15994</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2462; 18667</t>
+          <t>3294; 19559</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5961</t>
+          <t>0; 5116</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1957,32 +1957,32 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4594</t>
+          <t>0; 5383</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>488; 5513</t>
+          <t>543; 5853</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>925; 8263</t>
+          <t>917; 7705</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3931; 16809</t>
+          <t>3776; 16721</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3006; 15610</t>
+          <t>3083; 15303</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4181; 20451</t>
+          <t>5860; 24033</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>1629</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2948</t>
+          <t>4127</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3840</t>
+          <t>5756</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4906</t>
+          <t>0; 5652</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4086</t>
+          <t>0; 5046</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>943; 10049</t>
+          <t>939; 9742</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3878</t>
+          <t>0; 5713</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 7108</t>
+          <t>0; 7579</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 6696</t>
+          <t>0; 7526</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 6925</t>
+          <t>0; 5169</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>975; 7314</t>
+          <t>1419; 8716</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>948; 8336</t>
+          <t>0; 8105</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>987; 8589</t>
+          <t>996; 9695</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1843; 10935</t>
+          <t>1876; 11448</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1612; 7663</t>
+          <t>2718; 10585</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4176</t>
+          <t>6262</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4176</t>
+          <t>6262</t>
         </is>
       </c>
     </row>
@@ -2343,22 +2343,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 6374</t>
+          <t>0; 5521</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8745; 25577</t>
+          <t>8354; 25664</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2858; 12701</t>
+          <t>2185; 12274</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1120; 9990</t>
+          <t>1931; 15699</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 6686</t>
+          <t>0; 6461</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -2383,22 +2383,22 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 5945</t>
+          <t>0; 6286</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8383; 25235</t>
+          <t>8023; 25054</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3823; 15974</t>
+          <t>3810; 15193</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1353; 11458</t>
+          <t>2245; 15172</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11632</t>
+          <t>10311</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>4167</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>13658</t>
+          <t>14478</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3703; 17902</t>
+          <t>4300; 17793</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14039; 34065</t>
+          <t>13300; 33790</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8645; 26605</t>
+          <t>8602; 26555</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5567; 22316</t>
+          <t>5117; 18937</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>903; 8440</t>
+          <t>936; 8863</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 4904</t>
+          <t>0; 5193</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>995; 9543</t>
+          <t>998; 8634</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 6744</t>
+          <t>1053; 13584</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6657; 22701</t>
+          <t>5814; 21126</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14167; 34599</t>
+          <t>14729; 33689</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12013; 30564</t>
+          <t>11503; 30723</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5811; 24855</t>
+          <t>8379; 26973</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>8225</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2771</t>
+          <t>2930</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9512</t>
+          <t>11155</t>
         </is>
       </c>
     </row>
@@ -2759,32 +2759,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4343</t>
+          <t>0; 3725</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1748; 9970</t>
+          <t>1717; 10550</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2279; 12394</t>
+          <t>2106; 13048</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3092; 13058</t>
+          <t>3784; 15377</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 6873</t>
+          <t>0; 7633</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 7538</t>
+          <t>0; 7769</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2794,34 +2794,34 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>981; 6233</t>
+          <t>1187; 6490</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>907; 9298</t>
+          <t>904; 8343</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2787; 13034</t>
+          <t>2786; 13301</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2286; 12645</t>
+          <t>2234; 12745</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5734; 16521</t>
+          <t>6186; 18617</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2228</t>
+          <t>2224</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2228</t>
+          <t>2224</t>
         </is>
       </c>
     </row>
@@ -2967,17 +2967,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 6641</t>
+          <t>0; 6038</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2955; 13819</t>
+          <t>2976; 12986</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>969; 9540</t>
+          <t>951; 9313</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2987,42 +2987,42 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 5072</t>
+          <t>0; 6795</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 5813</t>
+          <t>0; 6218</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1019; 9083</t>
+          <t>940; 8682</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 11404</t>
+          <t>0; 11629</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 7371</t>
+          <t>0; 7347</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4055; 16872</t>
+          <t>4778; 17590</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3615; 14141</t>
+          <t>3615; 13868</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 10555</t>
+          <t>0; 11279</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>30786</t>
+          <t>35492</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>11915</t>
+          <t>15453</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>42701</t>
+          <t>50945</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>8948; 25199</t>
+          <t>8726; 24920</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>44044; 76677</t>
+          <t>44134; 78667</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>30077; 56671</t>
+          <t>31055; 58829</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>20221; 47255</t>
+          <t>23855; 53011</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4583; 18108</t>
+          <t>4926; 17607</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2974; 13654</t>
+          <t>2996; 14555</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5975; 19137</t>
+          <t>6730; 19820</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>5560; 21367</t>
+          <t>9423; 25308</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>15911; 36824</t>
+          <t>15914; 36317</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>49438; 82172</t>
+          <t>50176; 84006</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>40081; 69770</t>
+          <t>41155; 70036</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>28806; 59548</t>
+          <t>37995; 70272</t>
         </is>
       </c>
     </row>
